--- a/ksoft_old/docs/records/Carrier_Records.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records.xlsx
@@ -14280,13 +14280,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36134A9E-6B18-4B80-9F5F-C51D02A5FE8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A345AC-FDE4-49E1-8C3A-8887CA92A656}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D9B2D6-2C7A-4153-97E3-360CD89B56E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DBE73E-59C7-44D4-81D1-66300CA411F1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC2D29D7-1323-41DE-8C2A-C3D505BC8DFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B302264-F94F-42CC-8C27-37B082157710}"/>
 </file>
--- a/ksoft_old/docs/records/Carrier_Records.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records.xlsx
@@ -14280,13 +14280,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A345AC-FDE4-49E1-8C3A-8887CA92A656}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBB3766D-DD36-4671-937D-AD2BBB45C171}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DBE73E-59C7-44D4-81D1-66300CA411F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A50979-BF2A-4AE0-9E5F-67E96BEDB64F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B302264-F94F-42CC-8C27-37B082157710}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE56EFA-1663-4E97-9A3E-84F3CC2E5919}"/>
 </file>
--- a/ksoft_old/docs/records/Carrier_Records.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records.xlsx
@@ -14280,13 +14280,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBB3766D-DD36-4671-937D-AD2BBB45C171}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36134A9E-6B18-4B80-9F5F-C51D02A5FE8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A50979-BF2A-4AE0-9E5F-67E96BEDB64F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D9B2D6-2C7A-4153-97E3-360CD89B56E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE56EFA-1663-4E97-9A3E-84F3CC2E5919}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC2D29D7-1323-41DE-8C2A-C3D505BC8DFA}"/>
 </file>